--- a/data/trans_dic/P32A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,28</t>
+          <t>0,68; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,83</t>
+          <t>0,33; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,25</t>
+          <t>0,78; 3,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,49</t>
+          <t>0,09; 3,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,98</t>
+          <t>0,64; 3,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,06</t>
+          <t>0,45; 3,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,12</t>
+          <t>0,76; 3,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,11</t>
+          <t>0,43; 3,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,53</t>
+          <t>0,37; 5,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,45</t>
+          <t>0,37; 3,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,69</t>
+          <t>0,08; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,63</t>
+          <t>0,59; 5,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,78</t>
+          <t>0,75; 5,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,2</t>
+          <t>0,26; 2,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,59</t>
+          <t>0,3; 3,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,22</t>
+          <t>0,73; 3,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,64</t>
+          <t>0,56; 2,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,11</t>
+          <t>0,52; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,36</t>
+          <t>1,69; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,55</t>
+          <t>0,99; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,79</t>
+          <t>0,75; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,74</t>
+          <t>0,44; 2,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,08</t>
+          <t>1,47; 5,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,18</t>
+          <t>1,02; 4,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,71</t>
+          <t>0,62; 3,48</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,55</t>
+          <t>0,68; 2,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,95</t>
+          <t>1,38; 4,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,98</t>
+          <t>0,83; 3,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,09</t>
+          <t>1,29; 3,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,1</t>
+          <t>0,04; 1,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,05</t>
+          <t>0,54; 2,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,13</t>
+          <t>1,17; 3,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,2</t>
+          <t>0,61; 2,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,7</t>
+          <t>0,67; 2,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,13</t>
+          <t>1,58; 5,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,17</t>
+          <t>1,76; 6,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,48</t>
+          <t>0,9; 4,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,33</t>
+          <t>0,66; 4,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,8</t>
+          <t>0,27; 2,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,72</t>
+          <t>1,22; 3,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,13</t>
+          <t>1,28; 4,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,63</t>
+          <t>1,2; 3,57</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,91</t>
+          <t>0,69; 6,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,75</t>
+          <t>0,65; 6,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,68</t>
+          <t>0,73; 4,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,66</t>
+          <t>0,7; 4,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,15</t>
+          <t>1,15; 4,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,64</t>
+          <t>0,67; 1,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,34</t>
+          <t>1,88; 3,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,73</t>
+          <t>1,43; 2,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,58</t>
+          <t>1,25; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,77</t>
+          <t>0,39; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,24</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,15</t>
+          <t>0,59; 2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,27</t>
+          <t>0,53; 1,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,56</t>
+          <t>1,47; 2,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,27</t>
+          <t>1,36; 2,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,15</t>
+          <t>1,08; 2,13</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4664</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2652; 12566</t>
+          <t>2002; 11691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>955; 8167</t>
+          <t>949; 8061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2398; 11916</t>
+          <t>2197; 10850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5027</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 10626</t>
+          <t>0; 9139</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>489; 5513</t>
+          <t>136; 6173</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4619</t>
+          <t>0; 4626</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2838; 13122</t>
+          <t>2811; 13807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1949; 13539</t>
+          <t>1970; 13661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3717; 13662</t>
+          <t>3334; 13296</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>971; 9178</t>
+          <t>957; 7900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>926; 14029</t>
+          <t>947; 13482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>921; 8248</t>
+          <t>895; 8122</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169; 5691</t>
+          <t>167; 6003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5749</t>
+          <t>0; 8486</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1167; 10779</t>
+          <t>1122; 10523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>976; 6304</t>
+          <t>991; 7216</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956; 8285</t>
+          <t>970; 8340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1844; 14215</t>
+          <t>1206; 14834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2979; 13876</t>
+          <t>3150; 15116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1878; 9055</t>
+          <t>1924; 9234</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1715; 10543</t>
+          <t>1753; 10574</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7054; 24621</t>
+          <t>6545; 23325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3113; 15128</t>
+          <t>3301; 14572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1604; 10124</t>
+          <t>1584; 9281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5367</t>
+          <t>0; 5764</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1768; 10986</t>
+          <t>1768; 10274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6735; 23720</t>
+          <t>6879; 23998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3832; 16193</t>
+          <t>3965; 16418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1548; 9339</t>
+          <t>1557; 8768</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4673; 17044</t>
+          <t>4526; 18806</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9106; 26064</t>
+          <t>9082; 26430</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5555; 19602</t>
+          <t>5486; 20206</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6089; 20768</t>
+          <t>6538; 19806</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 5903</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4785</t>
+          <t>0; 5579</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>239; 8660</t>
+          <t>180; 7965</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4020; 17644</t>
+          <t>4655; 17244</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10231; 27799</t>
+          <t>10424; 28705</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6456; 21036</t>
+          <t>5794; 20909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6461; 24851</t>
+          <t>6214; 24634</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6970</t>
+          <t>0; 7115</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3944; 15555</t>
+          <t>4801; 16421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5507; 19526</t>
+          <t>5580; 20264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2196; 10347</t>
+          <t>2072; 10847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6747</t>
+          <t>0; 6026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 8170</t>
+          <t>0; 7487</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5943</t>
+          <t>0; 4862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>875; 5677</t>
+          <t>861; 5475</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1023; 9996</t>
+          <t>976; 9814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5938; 18096</t>
+          <t>5936; 18898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6417; 20968</t>
+          <t>6484; 20961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4051; 13139</t>
+          <t>4344; 12933</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1858</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>908; 9493</t>
+          <t>953; 8755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>946; 9261</t>
+          <t>1051; 9864</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 5072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 10749</t>
+          <t>0; 10548</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1879; 11919</t>
+          <t>1862; 11496</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11422</t>
+          <t>0; 11404</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 6284</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2751; 14608</t>
+          <t>2815; 17042</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4824; 17266</t>
+          <t>4763; 17170</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 11196</t>
+          <t>0; 10555</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12915; 30712</t>
+          <t>12543; 31305</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38773; 67996</t>
+          <t>38286; 71007</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27803; 54415</t>
+          <t>28526; 54432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19028; 39613</t>
+          <t>19149; 37775</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>924; 7924</t>
+          <t>920; 7988</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4025; 18491</t>
+          <t>4081; 16881</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8631; 25641</t>
+          <t>9004; 25869</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5642; 21417</t>
+          <t>5850; 22288</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15005; 35177</t>
+          <t>14751; 34156</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45064; 78668</t>
+          <t>45245; 78165</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41560; 71154</t>
+          <t>42714; 72907</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26444; 54499</t>
+          <t>27418; 53868</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,98</t>
+          <t>0,66; 4,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,79</t>
+          <t>0,33; 3,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,87</t>
+          <t>0,96; 4,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,9</t>
+          <t>0,31; 3,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,14</t>
+          <t>0,8; 3,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,45; 2,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,03</t>
+          <t>0,92; 3,29</t>
         </is>
       </c>
     </row>
@@ -804,19 +804,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,54</t>
+          <t>0,44; 3,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,32</t>
+          <t>0,37; 5,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,38; 3,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,84</t>
+          <t>0,31; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,5</t>
+          <t>0,58; 5,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,47</t>
+          <t>1,08; 5,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,75</t>
+          <t>0,48; 4,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,51</t>
+          <t>0,71; 3,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,69</t>
+          <t>0,84; 3,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,12</t>
+          <t>0,52; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,02</t>
+          <t>1,79; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,38</t>
+          <t>1,01; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,39</t>
+          <t>0,69; 4,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,57</t>
+          <t>0,45; 2,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,14</t>
+          <t>1,5; 5,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,24</t>
+          <t>1,04; 4,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,48</t>
+          <t>0,58; 3,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,81</t>
+          <t>0,69; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,01</t>
+          <t>1,36; 3,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,07</t>
+          <t>0,87; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,9</t>
+          <t>1,06; 3,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,93</t>
+          <t>1,01; 7,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,0</t>
+          <t>0,54; 2,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,23</t>
+          <t>1,2; 3,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,19</t>
+          <t>0,66; 2,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,68</t>
+          <t>1,41; 3,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,42</t>
+          <t>1,52; 5,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,4</t>
+          <t>1,69; 6,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,69</t>
+          <t>0,84; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,18</t>
+          <t>0,67; 3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,75</t>
+          <t>0,28; 2,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,89</t>
+          <t>1,1; 3,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,13</t>
+          <t>1,24; 4,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,57</t>
+          <t>0,96; 3,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,38</t>
+          <t>0,66; 6,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,13</t>
+          <t>0,65; 6,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,51</t>
+          <t>0,75; 4,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,27</t>
+          <t>0,72; 3,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,13</t>
+          <t>1,1; 4,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,67</t>
+          <t>0,67; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,49</t>
+          <t>1,91; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,73</t>
+          <t>1,41; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,46</t>
+          <t>1,22; 2,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,62</t>
+          <t>0,33; 1,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,26</t>
+          <t>0,8; 2,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,24</t>
+          <t>1,21; 3,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,23</t>
+          <t>0,54; 1,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,54</t>
+          <t>1,5; 2,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,32</t>
+          <t>1,31; 2,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,13</t>
+          <t>1,42; 2,51</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>8631</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4664</t>
+          <t>0; 5072</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2002; 11691</t>
+          <t>1944; 11917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>949; 8061</t>
+          <t>953; 9803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2197; 10850</t>
+          <t>2885; 13395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9139</t>
+          <t>0; 9820</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>136; 6173</t>
+          <t>536; 6118</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 3979</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2811; 13807</t>
+          <t>3515; 14757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1970; 13661</t>
+          <t>1970; 12963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3334; 13296</t>
+          <t>4340; 15517</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>6624</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>957; 7900</t>
+          <t>973; 8759</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>947; 13482</t>
+          <t>935; 14081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>895; 8122</t>
+          <t>912; 8632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167; 6003</t>
+          <t>683; 7289</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,37 +2160,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 8486</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1122; 10523</t>
+          <t>1107; 11081</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>991; 7216</t>
+          <t>1550; 8563</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>970; 8340</t>
+          <t>962; 8322</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1206; 14834</t>
+          <t>1894; 16684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3150; 15116</t>
+          <t>3052; 15436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1924; 9234</t>
+          <t>3081; 12084</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4151</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1753; 10574</t>
+          <t>1759; 10280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6545; 23325</t>
+          <t>6928; 24748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3301; 14572</t>
+          <t>3347; 15567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1584; 9281</t>
+          <t>1566; 9203</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5764</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1768; 10274</t>
+          <t>1791; 10114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6879; 23998</t>
+          <t>6991; 24110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3965; 16418</t>
+          <t>4026; 16575</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1557; 8768</t>
+          <t>1597; 9018</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>17986</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4526; 18806</t>
+          <t>4610; 17392</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9082; 26430</t>
+          <t>8961; 25037</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5486; 20206</t>
+          <t>5711; 21316</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6538; 19806</t>
+          <t>5726; 20245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5903</t>
+          <t>0; 6246</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 6761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>180; 7965</t>
+          <t>2303; 16203</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4655; 17244</t>
+          <t>4652; 17729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10424; 28705</t>
+          <t>10660; 28294</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5794; 20909</t>
+          <t>6346; 21456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6214; 24634</t>
+          <t>10821; 29830</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7630</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7115</t>
+          <t>0; 6539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4801; 16421</t>
+          <t>4610; 17207</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5580; 20264</t>
+          <t>5362; 19145</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2072; 10847</t>
+          <t>2148; 10132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6026</t>
+          <t>0; 6424</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7487</t>
+          <t>0; 7117</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4862</t>
+          <t>0; 5517</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>861; 5475</t>
+          <t>1027; 5773</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>976; 9814</t>
+          <t>986; 9448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5936; 18898</t>
+          <t>5345; 18495</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6484; 20961</t>
+          <t>6296; 21582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4344; 12933</t>
+          <t>3955; 12607</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>953; 8755</t>
+          <t>900; 8637</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1051; 9864</t>
+          <t>1054; 9848</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 6795</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 10548</t>
+          <t>0; 10383</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1862; 11496</t>
+          <t>1899; 11218</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11404</t>
+          <t>0; 11629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6284</t>
+          <t>0; 6156</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2815; 17042</t>
+          <t>2883; 14342</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4763; 17170</t>
+          <t>4578; 16678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 10555</t>
+          <t>0; 11279</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>47245</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12543; 31305</t>
+          <t>12666; 31506</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38286; 71007</t>
+          <t>38881; 70228</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28526; 54432</t>
+          <t>28102; 53575</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19149; 37775</t>
+          <t>20020; 40909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>920; 7988</t>
+          <t>924; 8006</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4081; 16881</t>
+          <t>3421; 17827</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9004; 25869</t>
+          <t>9097; 26122</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5850; 22288</t>
+          <t>10482; 28448</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14751; 34156</t>
+          <t>14943; 34915</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45245; 78165</t>
+          <t>46166; 79157</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42714; 72907</t>
+          <t>41127; 72436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27418; 53868</t>
+          <t>35627; 62884</t>
         </is>
       </c>
     </row>
